--- a/agile-dashboard.xlsx
+++ b/agile-dashboard.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinee\Documents\Data analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{99587D00-8B42-411F-9D22-033D060A6CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD75D84E-5C22-4D29-AA89-26CBEFB38C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9719B9AB-A075-435C-99AA-28E7CDD74CB6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9719B9AB-A075-435C-99AA-28E7CDD74CB6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
+    <sheet name="Analysis data" sheetId="2" r:id="rId1"/>
     <sheet name="Burndown -sprint 1" sheetId="3" r:id="rId2"/>
     <sheet name="Agile Performance Dashboard" sheetId="6" r:id="rId3"/>
     <sheet name="Raw data " sheetId="1" r:id="rId4"/>
@@ -23,7 +23,6 @@
     <pivotCache cacheId="0" r:id="rId5"/>
     <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -810,7 +809,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Agile Performance Dashboard.xlsx]Dashboard!PivotTable1</c:name>
+    <c:name>[agile-dashboard.xlsx]Analysis data!PivotTable1</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -939,7 +938,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$3</c:f>
+              <c:f>'Analysis data'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -960,7 +959,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$4:$A$12</c:f>
+              <c:f>'Analysis data'!$A$4:$A$12</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -992,7 +991,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$4:$B$12</c:f>
+              <c:f>'Analysis data'!$B$4:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -1766,7 +1765,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Agile Performance Dashboard.xlsx]Dashboard!PivotTable2</c:name>
+    <c:name>[agile-dashboard.xlsx]Analysis data!PivotTable2</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1894,7 +1893,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$25</c:f>
+              <c:f>'Analysis data'!$B$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1917,7 +1916,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$26:$A$34</c:f>
+              <c:f>'Analysis data'!$A$26:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -1949,7 +1948,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$26:$B$34</c:f>
+              <c:f>'Analysis data'!$B$26:$B$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2285,7 +2284,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$62</c:f>
+              <c:f>'Analysis data'!$B$62</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2337,11 +2336,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Dashboard!$A$63:$A$71</c15:sqref>
+                    <c15:sqref>'Analysis data'!$A$63:$A$71</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Dashboard!$A$63:$A$70</c:f>
+              <c:f>'Analysis data'!$A$63:$A$70</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2376,11 +2375,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Dashboard!$B$63:$B$71</c15:sqref>
+                    <c15:sqref>'Analysis data'!$B$63:$B$71</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Dashboard!$B$63:$B$70</c:f>
+              <c:f>'Analysis data'!$B$63:$B$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2671,7 +2670,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$92</c:f>
+              <c:f>'Analysis data'!$B$92</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2692,7 +2691,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$93:$A$100</c:f>
+              <c:f>'Analysis data'!$A$93:$A$100</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2724,7 +2723,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$93:$B$100</c:f>
+              <c:f>'Analysis data'!$B$93:$B$100</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3021,7 +3020,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$45</c:f>
+              <c:f>'Analysis data'!$B$45</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3042,7 +3041,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$46:$A$53</c:f>
+              <c:f>'Analysis data'!$A$46:$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3074,7 +3073,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$46:$B$53</c:f>
+              <c:f>'Analysis data'!$B$46:$B$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3132,7 +3131,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$C$45</c:f>
+              <c:f>'Analysis data'!$C$45</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3155,7 +3154,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$46:$A$53</c:f>
+              <c:f>'Analysis data'!$A$46:$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3187,7 +3186,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$C$46:$C$53</c:f>
+              <c:f>'Analysis data'!$C$46:$C$53</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4164,7 +4163,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$45</c:f>
+              <c:f>'Analysis data'!$B$45</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4185,7 +4184,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$46:$A$53</c:f>
+              <c:f>'Analysis data'!$A$46:$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4217,7 +4216,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$46:$B$53</c:f>
+              <c:f>'Analysis data'!$B$46:$B$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4275,7 +4274,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$C$45</c:f>
+              <c:f>'Analysis data'!$C$45</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4298,7 +4297,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$46:$A$53</c:f>
+              <c:f>'Analysis data'!$A$46:$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4330,7 +4329,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$C$46:$C$53</c:f>
+              <c:f>'Analysis data'!$C$46:$C$53</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4648,7 +4647,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$62</c:f>
+              <c:f>'Analysis data'!$B$62</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4700,11 +4699,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Dashboard!$A$63:$A$71</c15:sqref>
+                    <c15:sqref>'Analysis data'!$A$63:$A$71</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Dashboard!$A$63:$A$70</c:f>
+              <c:f>'Analysis data'!$A$63:$A$70</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4739,11 +4738,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Dashboard!$B$63:$B$71</c15:sqref>
+                    <c15:sqref>'Analysis data'!$B$63:$B$71</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Dashboard!$B$63:$B$70</c:f>
+              <c:f>'Analysis data'!$B$63:$B$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -5031,7 +5030,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$92</c:f>
+              <c:f>'Analysis data'!$B$92</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5052,7 +5051,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$93:$A$100</c:f>
+              <c:f>'Analysis data'!$A$93:$A$100</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -5084,7 +5083,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$93:$B$100</c:f>
+              <c:f>'Analysis data'!$B$93:$B$100</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
